--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,12 +35,8 @@
       <b val="1"/>
       <color rgb="00385723"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C65911"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,14 +82,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,11 +532,11 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5</v>
+        <v>1.36</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -584,11 +573,11 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -625,11 +614,11 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -666,11 +655,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,11 +696,11 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.4</v>
+        <v>0.97</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -748,11 +737,11 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -789,11 +778,11 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -830,11 +819,11 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.44</v>
+        <v>1.27</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -871,11 +860,11 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.24</v>
+        <v>0.33</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -912,11 +901,11 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -953,11 +942,11 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -994,11 +983,11 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1035,11 +1024,11 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1076,11 +1065,11 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1117,11 +1106,11 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.41</v>
+        <v>0.72</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1158,11 +1147,11 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1199,11 +1188,11 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.12</v>
+        <v>0.92</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1240,11 +1229,11 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.42</v>
+        <v>0.52</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1281,11 +1270,11 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1322,11 +1311,11 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1363,11 +1352,11 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1404,11 +1393,11 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1445,7 +1434,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
@@ -1486,11 +1475,11 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1527,11 +1516,11 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1568,11 +1557,11 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1.17</v>
+        <v>0.6</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1609,11 +1598,11 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1650,11 +1639,11 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.47</v>
+        <v>1.33</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1691,11 +1680,11 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1732,11 +1721,11 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1.05</v>
+        <v>0.71</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1773,11 +1762,11 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.85</v>
+        <v>1.26</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1814,11 +1803,11 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1855,11 +1844,11 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.21</v>
+        <v>0.72</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1896,11 +1885,11 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1937,11 +1926,11 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.4</v>
+        <v>1.29</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1978,11 +1967,11 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2019,11 +2008,11 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2060,11 +2049,11 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1.19</v>
+        <v>0.9</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2101,11 +2090,11 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2142,11 +2131,11 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2183,11 +2172,11 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1.22</v>
+        <v>0.55</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2224,11 +2213,11 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.29</v>
+        <v>1.44</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2265,11 +2254,11 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,24 +2293,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>AppiumDriverException: Touch target in Android Touch Gestures obstructed or unclickable.</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2351,11 +2336,11 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,11 +2377,11 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1.18</v>
+        <v>0.87</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,11 +2418,11 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2459,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
@@ -2515,11 +2500,11 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1.25</v>
+        <v>0.79</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,11 +2541,11 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.31</v>
+        <v>1.03</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,11 +2582,11 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1.25</v>
+        <v>0.29</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,11 +2623,11 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,11 +2664,11 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,11 +2705,11 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,11 +2746,11 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.68</v>
+        <v>1.21</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2802,11 +2787,11 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2843,11 +2828,11 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.18</v>
+        <v>0.49</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2884,11 +2869,11 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2925,11 +2910,11 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1.35</v>
+        <v>0.32</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2966,11 +2951,11 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1.16</v>
+        <v>0.45</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3007,11 +2992,11 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.28</v>
+        <v>1.15</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3048,11 +3033,11 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1.26</v>
+        <v>0.74</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3089,11 +3074,11 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3130,11 +3115,11 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.64</v>
+        <v>0.38</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3171,11 +3156,11 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1.38</v>
+        <v>0.7</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3212,11 +3197,11 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>1.25</v>
+        <v>0.42</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3253,11 +3238,11 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8</v>
+        <v>1.31</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3294,11 +3279,11 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.52</v>
+        <v>0.83</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3335,11 +3320,11 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3376,11 +3361,11 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3417,11 +3402,11 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3458,11 +3443,11 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.38</v>
+        <v>1.1</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3499,11 +3484,11 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.32</v>
+        <v>0.28</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3540,11 +3525,11 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3581,11 +3566,11 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3622,11 +3607,11 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3663,11 +3648,11 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3704,11 +3689,11 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3745,11 +3730,11 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.68</v>
+        <v>1.16</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3786,11 +3771,11 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,11 +3812,11 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,11 +3853,11 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,11 +3894,11 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.25</v>
+        <v>1.18</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,11 +3935,11 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,11 +3976,11 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,11 +4017,11 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,11 +4058,11 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>1.29</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,11 +4099,11 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.38</v>
+        <v>1.37</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4153,24 +4138,20 @@
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>AppiumDriverException: Touch target in Mobile Viewport Layout obstructed or unclickable.</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4200,11 +4181,11 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4241,11 +4222,11 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.3</v>
+        <v>0.64</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4282,11 +4263,11 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4323,11 +4304,11 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.62</v>
+        <v>1.12</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4364,11 +4345,11 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4405,11 +4386,11 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4446,11 +4427,11 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.47</v>
+        <v>1.24</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4487,11 +4468,11 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.61</v>
+        <v>0.88</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4528,11 +4509,11 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>1.17</v>
+        <v>0.77</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4569,11 +4550,11 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>1.2</v>
+        <v>0.61</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4610,11 +4591,11 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4651,11 +4632,11 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.89</v>
+        <v>0.3</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4692,11 +4673,11 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4733,11 +4714,11 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4774,11 +4755,11 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4815,11 +4796,11 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4856,11 +4837,11 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.91</v>
+        <v>1.22</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4897,11 +4878,11 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.29</v>
+        <v>0.73</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4938,11 +4919,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.35</v>
+        <v>0.92</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4979,11 +4960,11 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.63</v>
+        <v>0.36</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5020,11 +5001,11 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1.07</v>
+        <v>0.49</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5061,11 +5042,11 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.54</v>
+        <v>0.28</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5102,11 +5083,11 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.38</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5143,11 +5124,11 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5184,11 +5165,11 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5225,11 +5206,11 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.58</v>
+        <v>1.13</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5266,11 +5247,11 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.4</v>
+        <v>1.26</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5307,11 +5288,11 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5348,11 +5329,11 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.91</v>
+        <v>1.22</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5389,11 +5370,11 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5430,11 +5411,11 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.67</v>
+        <v>1.34</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5471,11 +5452,11 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.8</v>
+        <v>1.44</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5512,11 +5493,11 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5553,11 +5534,11 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.98</v>
+        <v>1.25</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5594,11 +5575,11 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5635,11 +5616,11 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.62</v>
+        <v>1.31</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5676,11 +5657,11 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5717,11 +5698,11 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.33</v>
+        <v>0.49</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5758,11 +5739,11 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.82</v>
+        <v>1.04</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5799,11 +5780,11 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5840,11 +5821,11 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1.19</v>
+        <v>0.87</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5881,11 +5862,11 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.86</v>
+        <v>0.35</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5922,11 +5903,11 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5963,11 +5944,11 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>1.06</v>
+        <v>0.49</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -6002,24 +5983,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>1.34</v>
+        <v>0.33</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>AppiumDriverException: Touch target in Mobile QR Camera Scanning obstructed or unclickable.</t>
-        </is>
-      </c>
+      <c r="I135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6049,11 +6026,11 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6090,11 +6067,11 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>1.37</v>
+        <v>0.45</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6131,11 +6108,11 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.95</v>
+        <v>0.58</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6172,11 +6149,11 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.43</v>
+        <v>1.39</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6213,11 +6190,11 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6254,11 +6231,11 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6295,11 +6272,11 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6336,11 +6313,11 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6377,11 +6354,11 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.7</v>
+        <v>1.37</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6418,11 +6395,11 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6459,11 +6436,11 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6500,11 +6477,11 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6541,11 +6518,11 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6582,11 +6559,11 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1.26</v>
+        <v>0.41</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6623,11 +6600,11 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6664,11 +6641,11 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6705,11 +6682,11 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.78</v>
+        <v>1.26</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6746,11 +6723,11 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.67</v>
+        <v>1.37</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6787,11 +6764,11 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6828,11 +6805,11 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6869,11 +6846,11 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6910,11 +6887,11 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.57</v>
+        <v>1.16</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6951,11 +6928,11 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6992,11 +6969,11 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7033,11 +7010,11 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.66</v>
+        <v>1.08</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7074,11 +7051,11 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.25</v>
+        <v>1.15</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7115,11 +7092,11 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.55</v>
+        <v>1.01</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7156,11 +7133,11 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.26</v>
+        <v>0.54</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7197,11 +7174,11 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.73</v>
+        <v>0.48</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7238,11 +7215,11 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7279,11 +7256,11 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>1.27</v>
+        <v>0.99</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7320,7 +7297,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G167" s="2" t="n">
@@ -7361,11 +7338,11 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7402,11 +7379,11 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7443,11 +7420,11 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7484,11 +7461,11 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7525,11 +7502,11 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1.26</v>
+        <v>0.4</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7566,11 +7543,11 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7607,11 +7584,11 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7648,11 +7625,11 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7689,11 +7666,11 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7730,11 +7707,11 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>1.24</v>
+        <v>0.91</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7771,11 +7748,11 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7812,11 +7789,11 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>1.32</v>
+        <v>0.54</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7851,24 +7828,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.76</v>
+        <v>1.33</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>AppiumDriverException: Touch target in Mobile Navigation Drawer obstructed or unclickable.</t>
-        </is>
-      </c>
+      <c r="I180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -7898,11 +7871,11 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.73</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7939,11 +7912,11 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7980,11 +7953,11 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8021,11 +7994,11 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8062,11 +8035,11 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8103,11 +8076,11 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.74</v>
+        <v>1.16</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8144,11 +8117,11 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>1.34</v>
+        <v>0.72</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8185,11 +8158,11 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.37</v>
+        <v>1.01</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8226,11 +8199,11 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8267,7 +8240,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G190" s="2" t="n">
@@ -8308,11 +8281,11 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8349,11 +8322,11 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8390,11 +8363,11 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.31</v>
+        <v>1.18</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8431,11 +8404,11 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8472,11 +8445,11 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8513,11 +8486,11 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8554,11 +8527,11 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.91</v>
+        <v>0.54</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8595,11 +8568,11 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.54</v>
+        <v>1.2</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8636,11 +8609,11 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.3</v>
+        <v>1.39</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8677,11 +8650,11 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.62</v>
+        <v>1.15</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8718,11 +8691,11 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>1.36</v>
+        <v>0.4</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8759,11 +8732,11 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8800,11 +8773,11 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8841,11 +8814,11 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.28</v>
+        <v>1.36</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8882,11 +8855,11 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.75</v>
+        <v>0.29</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8923,11 +8896,11 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.37</v>
+        <v>1.01</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8964,11 +8937,11 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -9005,11 +8978,11 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.97</v>
+        <v>1.37</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9046,11 +9019,11 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9087,11 +9060,11 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9128,11 +9101,11 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.3</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9169,11 +9142,11 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9210,11 +9183,11 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.36</v>
+        <v>1.32</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9251,11 +9224,11 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.35</v>
+        <v>1.18</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9292,11 +9265,11 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9333,11 +9306,11 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9374,11 +9347,11 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9415,11 +9388,11 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9456,11 +9429,11 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9497,11 +9470,11 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9538,11 +9511,11 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.3</v>
+        <v>1.06</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9579,11 +9552,11 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9620,11 +9593,11 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9661,11 +9634,11 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9700,24 +9673,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>1.37</v>
+        <v>0.84</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>AppiumDriverException: Touch target in Mobile Input Validation obstructed or unclickable.</t>
-        </is>
-      </c>
+      <c r="I225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -9747,11 +9716,11 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.27</v>
+        <v>0.77</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9788,11 +9757,11 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9829,11 +9798,11 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9870,11 +9839,11 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9911,11 +9880,11 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>1.29</v>
+        <v>0.65</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9952,11 +9921,11 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1.4</v>
+        <v>0.76</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9993,11 +9962,11 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.38</v>
+        <v>1.09</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10034,11 +10003,11 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10075,11 +10044,11 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10116,11 +10085,11 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10157,11 +10126,11 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.43</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10198,11 +10167,11 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.88</v>
+        <v>1.24</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10239,11 +10208,11 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.36</v>
+        <v>1.37</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10280,11 +10249,11 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1.24</v>
+        <v>0.5</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10321,11 +10290,11 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10362,11 +10331,11 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10403,11 +10372,11 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10444,11 +10413,11 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.29</v>
+        <v>1.41</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10485,11 +10454,11 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10526,11 +10495,11 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>1.27</v>
+        <v>0.77</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10567,11 +10536,11 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.76</v>
+        <v>0.35</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10608,11 +10577,11 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10649,11 +10618,11 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.6</v>
+        <v>1.09</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10690,11 +10659,11 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.83</v>
+        <v>0.31</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10731,11 +10700,11 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10772,11 +10741,11 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10813,11 +10782,11 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10854,11 +10823,11 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>1.43</v>
+        <v>0.86</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10895,11 +10864,11 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10936,11 +10905,11 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10977,11 +10946,11 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>1.07</v>
+        <v>0.37</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11018,11 +10987,11 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.74</v>
+        <v>1.29</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11059,11 +11028,11 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11100,11 +11069,11 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11141,11 +11110,11 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>1.41</v>
+        <v>0.9</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11182,11 +11151,11 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>1.38</v>
+        <v>0.25</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11223,11 +11192,11 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.99</v>
+        <v>1.41</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11264,11 +11233,11 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>1.27</v>
+        <v>0.8</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11305,11 +11274,11 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.39</v>
+        <v>0.87</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11346,11 +11315,11 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11387,11 +11356,11 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>1.38</v>
+        <v>0.86</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11428,11 +11397,11 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11469,11 +11438,11 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11510,11 +11479,11 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11549,24 +11518,20 @@
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="F270" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>1.05</v>
+        <v>0.45</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I270" s="2" t="inlineStr">
-        <is>
-          <t>AppiumDriverException: Touch target in Mobile Performance &amp; Memory obstructed or unclickable.</t>
-        </is>
-      </c>
+      <c r="I270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -11596,11 +11561,11 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11637,11 +11602,11 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11678,11 +11643,11 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.48</v>
+        <v>0.98</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11719,11 +11684,11 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.85</v>
+        <v>1.23</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11760,11 +11725,11 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.61</v>
+        <v>1.21</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11801,11 +11766,11 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>1.21</v>
+        <v>0.27</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11842,11 +11807,11 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.35</v>
+        <v>1.09</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11883,11 +11848,11 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>1.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11924,11 +11889,11 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>1.01</v>
+        <v>0.77</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11965,11 +11930,11 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>1.33</v>
+        <v>0.53</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -12006,11 +11971,11 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.48</v>
+        <v>1.29</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12047,11 +12012,11 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12088,11 +12053,11 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12129,11 +12094,11 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12170,11 +12135,11 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12211,11 +12176,11 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12252,11 +12217,11 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12293,11 +12258,11 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12334,11 +12299,11 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12375,11 +12340,11 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12416,11 +12381,11 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>1.27</v>
+        <v>0.34</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12457,11 +12422,11 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12498,11 +12463,11 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12539,11 +12504,11 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12580,11 +12545,11 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12621,11 +12586,11 @@
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.64</v>
+        <v>1.21</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12662,11 +12627,11 @@
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12703,11 +12668,11 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12744,11 +12709,11 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>1.11</v>
+        <v>0.4</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12785,11 +12750,11 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>1.26</v>
+        <v>0.98</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12826,11 +12791,11 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-001</t>
+          <t>TC_MOB_AUTH_001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.36</v>
+        <v>0.37</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-002</t>
+          <t>TC_MOB_AUTH_002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-003</t>
+          <t>TC_MOB_AUTH_003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-004</t>
+          <t>TC_MOB_AUTH_004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.48</v>
+        <v>1.07</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-005</t>
+          <t>TC_MOB_AUTH_005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-006</t>
+          <t>TC_MOB_AUTH_006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.99</v>
+        <v>1.27</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-007</t>
+          <t>TC_MOB_AUTH_007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-008</t>
+          <t>TC_MOB_AUTH_008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-009</t>
+          <t>TC_MOB_AUTH_009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.33</v>
+        <v>1.29</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-010</t>
+          <t>TC_MOB_AUTH_010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.38</v>
+        <v>1.33</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-011</t>
+          <t>TC_MOB_AUTH_011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-012</t>
+          <t>TC_MOB_AUTH_012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1.22</v>
+        <v>0.54</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-013</t>
+          <t>TC_MOB_AUTH_013</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-014</t>
+          <t>TC_MOB_AUTH_014</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.51</v>
+        <v>1.24</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-015</t>
+          <t>TC_MOB_AUTH_015</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-016</t>
+          <t>TC_MOB_AUTH_016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-017</t>
+          <t>TC_MOB_AUTH_017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-018</t>
+          <t>TC_MOB_AUTH_018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-019</t>
+          <t>TC_MOB_AUTH_019</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.48</v>
+        <v>1.01</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-020</t>
+          <t>TC_MOB_AUTH_020</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.48</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-021</t>
+          <t>TC_MOB_AUTH_021</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.3</v>
+        <v>1.41</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-022</t>
+          <t>TC_MOB_AUTH_022</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-023</t>
+          <t>TC_MOB_AUTH_023</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-024</t>
+          <t>TC_MOB_AUTH_024</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.41</v>
+        <v>0.98</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-025</t>
+          <t>TC_MOB_AUTH_025</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-026</t>
+          <t>TC_MOB_AUTH_026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.6</v>
+        <v>1.16</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-027</t>
+          <t>TC_MOB_AUTH_027</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.37</v>
+        <v>1.15</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-028</t>
+          <t>TC_MOB_AUTH_028</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-029</t>
+          <t>TC_MOB_AUTH_029</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.49</v>
+        <v>0.65</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-030</t>
+          <t>TC_MOB_AUTH_030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-031</t>
+          <t>TC_MOB_AUTH_031</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-032</t>
+          <t>TC_MOB_AUTH_032</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-033</t>
+          <t>TC_MOB_AUTH_033</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-034</t>
+          <t>TC_MOB_AUTH_034</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-035</t>
+          <t>TC_MOB_AUTH_035</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-036</t>
+          <t>TC_MOB_AUTH_036</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-037</t>
+          <t>TC_MOB_AUTH_037</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.12</v>
+        <v>0.6</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-038</t>
+          <t>TC_MOB_AUTH_038</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.9</v>
+        <v>0.37</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-039</t>
+          <t>TC_MOB_AUTH_039</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-040</t>
+          <t>TC_MOB_AUTH_040</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-041</t>
+          <t>TC_MOB_GEST_001</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-042</t>
+          <t>TC_MOB_GEST_002</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-043</t>
+          <t>TC_MOB_GEST_003</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.88</v>
+        <v>1.42</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-044</t>
+          <t>TC_MOB_GEST_004</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-045</t>
+          <t>TC_MOB_GEST_005</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.59</v>
+        <v>1.16</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-046</t>
+          <t>TC_MOB_GEST_006</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-047</t>
+          <t>TC_MOB_GEST_007</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-048</t>
+          <t>TC_MOB_GEST_008</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.93</v>
+        <v>1.33</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-049</t>
+          <t>TC_MOB_GEST_009</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.79</v>
+        <v>1.27</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-050</t>
+          <t>TC_MOB_GEST_010</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.03</v>
+        <v>0.8</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-051</t>
+          <t>TC_MOB_GEST_011</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.29</v>
+        <v>0.74</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-052</t>
+          <t>TC_MOB_GEST_012</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.74</v>
+        <v>1.12</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-053</t>
+          <t>TC_MOB_GEST_013</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.27</v>
+        <v>0.85</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-054</t>
+          <t>TC_MOB_GEST_014</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.98</v>
+        <v>0.33</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-055</t>
+          <t>TC_MOB_GEST_015</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1.21</v>
+        <v>0.66</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-056</t>
+          <t>TC_MOB_GEST_016</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-057</t>
+          <t>TC_MOB_GEST_017</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-058</t>
+          <t>TC_MOB_GEST_018</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1.13</v>
+        <v>0.41</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-059</t>
+          <t>TC_MOB_GEST_019</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.32</v>
+        <v>1.03</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-060</t>
+          <t>TC_MOB_GEST_020</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.45</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-061</t>
+          <t>TC_MOB_GEST_021</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-062</t>
+          <t>TC_MOB_GEST_022</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.74</v>
+        <v>0.3</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-063</t>
+          <t>TC_MOB_GEST_023</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.12</v>
+        <v>0.61</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-064</t>
+          <t>TC_MOB_GEST_024</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.38</v>
+        <v>1.12</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-065</t>
+          <t>TC_MOB_GEST_025</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-066</t>
+          <t>TC_MOB_GEST_026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-067</t>
+          <t>TC_MOB_GEST_027</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1.31</v>
+        <v>0.26</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-068</t>
+          <t>TC_MOB_GEST_028</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-069</t>
+          <t>TC_MOB_GEST_029</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-070</t>
+          <t>TC_MOB_GEST_030</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-071</t>
+          <t>TC_MOB_GEST_031</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-072</t>
+          <t>TC_MOB_GEST_032</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-073</t>
+          <t>TC_MOB_GEST_033</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.28</v>
+        <v>0.93</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-074</t>
+          <t>TC_MOB_GEST_034</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-075</t>
+          <t>TC_MOB_GEST_035</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-076</t>
+          <t>TC_MOB_GEST_036</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-077</t>
+          <t>TC_MOB_GEST_037</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.4</v>
+        <v>1.02</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-078</t>
+          <t>TC_MOB_GEST_038</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1.3</v>
+        <v>0.38</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-079</t>
+          <t>TC_MOB_GEST_039</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-080</t>
+          <t>TC_MOB_GEST_040</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-081</t>
+          <t>TC_MOB_LAYOUT_001</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.08</v>
+        <v>0.42</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-082</t>
+          <t>TC_MOB_LAYOUT_002</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.86</v>
+        <v>1.28</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-083</t>
+          <t>TC_MOB_LAYOUT_003</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1.18</v>
+        <v>0.68</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-084</t>
+          <t>TC_MOB_LAYOUT_004</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-085</t>
+          <t>TC_MOB_LAYOUT_005</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-086</t>
+          <t>TC_MOB_LAYOUT_006</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-087</t>
+          <t>TC_MOB_LAYOUT_007</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.65</v>
+        <v>1.44</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-088</t>
+          <t>TC_MOB_LAYOUT_008</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>1.37</v>
+        <v>0.96</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-089</t>
+          <t>TC_MOB_LAYOUT_009</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.96</v>
+        <v>1.23</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-090</t>
+          <t>TC_MOB_LAYOUT_010</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.72</v>
+        <v>1.02</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-091</t>
+          <t>TC_MOB_LAYOUT_011</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-092</t>
+          <t>TC_MOB_LAYOUT_012</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1.42</v>
+        <v>0.85</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-093</t>
+          <t>TC_MOB_LAYOUT_013</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-094</t>
+          <t>TC_MOB_LAYOUT_014</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1.13</v>
+        <v>0.62</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-095</t>
+          <t>TC_MOB_LAYOUT_015</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-096</t>
+          <t>TC_MOB_LAYOUT_016</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-097</t>
+          <t>TC_MOB_LAYOUT_017</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.88</v>
+        <v>0.48</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-098</t>
+          <t>TC_MOB_LAYOUT_018</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.77</v>
+        <v>1.42</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-099</t>
+          <t>TC_MOB_LAYOUT_019</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-100</t>
+          <t>TC_MOB_LAYOUT_020</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.97</v>
+        <v>0.55</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-101</t>
+          <t>TC_MOB_LAYOUT_021</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.3</v>
+        <v>1.27</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-102</t>
+          <t>TC_MOB_LAYOUT_022</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.73</v>
+        <v>1.1</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-103</t>
+          <t>TC_MOB_LAYOUT_023</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1.09</v>
+        <v>0.41</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-104</t>
+          <t>TC_MOB_LAYOUT_024</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.27</v>
+        <v>1.11</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-105</t>
+          <t>TC_MOB_LAYOUT_025</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-106</t>
+          <t>TC_MOB_LAYOUT_026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>1.22</v>
+        <v>0.9</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-107</t>
+          <t>TC_MOB_LAYOUT_027</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-108</t>
+          <t>TC_MOB_LAYOUT_028</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.92</v>
+        <v>0.34</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-109</t>
+          <t>TC_MOB_LAYOUT_029</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.36</v>
+        <v>1.26</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-110</t>
+          <t>TC_MOB_LAYOUT_030</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.49</v>
+        <v>0.83</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-111</t>
+          <t>TC_MOB_LAYOUT_031</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-112</t>
+          <t>TC_MOB_LAYOUT_032</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-113</t>
+          <t>TC_MOB_LAYOUT_033</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-114</t>
+          <t>TC_MOB_LAYOUT_034</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-115</t>
+          <t>TC_MOB_LAYOUT_035</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-116</t>
+          <t>TC_MOB_LAYOUT_036</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>1.26</v>
+        <v>0.52</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-117</t>
+          <t>TC_MOB_LAYOUT_037</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-118</t>
+          <t>TC_MOB_LAYOUT_038</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>1.22</v>
+        <v>0.54</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-119</t>
+          <t>TC_MOB_LAYOUT_039</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-120</t>
+          <t>TC_MOB_LAYOUT_040</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1.34</v>
+        <v>0.29</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-121</t>
+          <t>TC_MOB_QR_001</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>1.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-122</t>
+          <t>TC_MOB_QR_002</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.21</v>
+        <v>0.61</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-123</t>
+          <t>TC_MOB_QR_003</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>1.25</v>
+        <v>0.65</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-124</t>
+          <t>TC_MOB_QR_004</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-125</t>
+          <t>TC_MOB_QR_005</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>1.31</v>
+        <v>0.31</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-126</t>
+          <t>TC_MOB_QR_006</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-127</t>
+          <t>TC_MOB_QR_007</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-128</t>
+          <t>TC_MOB_QR_008</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>1.04</v>
+        <v>0.49</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-129</t>
+          <t>TC_MOB_QR_009</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-130</t>
+          <t>TC_MOB_QR_010</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.87</v>
+        <v>1.33</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-131</t>
+          <t>TC_MOB_QR_011</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.35</v>
+        <v>0.49</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-132</t>
+          <t>TC_MOB_QR_012</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-133</t>
+          <t>TC_MOB_QR_013</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-134</t>
+          <t>TC_MOB_QR_014</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-135</t>
+          <t>TC_MOB_QR_015</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-136</t>
+          <t>TC_MOB_QR_016</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-137</t>
+          <t>TC_MOB_QR_017</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.58</v>
+        <v>1.42</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-138</t>
+          <t>TC_MOB_QR_018</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-139</t>
+          <t>TC_MOB_QR_019</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.49</v>
+        <v>1.27</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-140</t>
+          <t>TC_MOB_QR_020</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-141</t>
+          <t>TC_MOB_QR_021</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.88</v>
+        <v>1.37</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-142</t>
+          <t>TC_MOB_QR_022</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-143</t>
+          <t>TC_MOB_QR_023</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1.37</v>
+        <v>0.99</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-144</t>
+          <t>TC_MOB_QR_024</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-145</t>
+          <t>TC_MOB_QR_025</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-146</t>
+          <t>TC_MOB_QR_026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-147</t>
+          <t>TC_MOB_QR_027</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-148</t>
+          <t>TC_MOB_QR_028</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-149</t>
+          <t>TC_MOB_QR_029</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-150</t>
+          <t>TC_MOB_QR_030</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-151</t>
+          <t>TC_MOB_QR_031</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1.26</v>
+        <v>0.47</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-152</t>
+          <t>TC_MOB_QR_032</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-153</t>
+          <t>TC_MOB_QR_033</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-154</t>
+          <t>TC_MOB_QR_034</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-155</t>
+          <t>TC_MOB_QR_035</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.77</v>
+        <v>0.44</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-156</t>
+          <t>TC_MOB_NAV_001</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-157</t>
+          <t>TC_MOB_NAV_002</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.72</v>
+        <v>1.26</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-158</t>
+          <t>TC_MOB_NAV_003</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-159</t>
+          <t>TC_MOB_NAV_004</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-160</t>
+          <t>TC_MOB_NAV_005</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-161</t>
+          <t>TC_MOB_NAV_006</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>1.01</v>
+        <v>0.65</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-162</t>
+          <t>TC_MOB_NAV_007</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-163</t>
+          <t>TC_MOB_NAV_008</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-164</t>
+          <t>TC_MOB_NAV_009</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-165</t>
+          <t>TC_MOB_NAV_010</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.99</v>
+        <v>1.38</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-166</t>
+          <t>TC_MOB_NAV_011</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-167</t>
+          <t>TC_MOB_NAV_012</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-168</t>
+          <t>TC_MOB_NAV_013</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-169</t>
+          <t>TC_MOB_NAV_014</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-170</t>
+          <t>TC_MOB_NAV_015</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-171</t>
+          <t>TC_MOB_NAV_016</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-172</t>
+          <t>TC_MOB_NAV_017</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-173</t>
+          <t>TC_MOB_NAV_018</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>1.13</v>
+        <v>0.64</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-174</t>
+          <t>TC_MOB_NAV_019</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.41</v>
+        <v>1.28</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-175</t>
+          <t>TC_MOB_NAV_020</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-176</t>
+          <t>TC_MOB_NAV_021</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-177</t>
+          <t>TC_MOB_NAV_022</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.78</v>
+        <v>1.15</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-178</t>
+          <t>TC_MOB_NAV_023</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-179</t>
+          <t>TC_MOB_NAV_024</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1.33</v>
+        <v>0.87</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-180</t>
+          <t>TC_MOB_NAV_025</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-181</t>
+          <t>TC_MOB_NAV_026</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.83</v>
+        <v>1.41</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-182</t>
+          <t>TC_MOB_NAV_027</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-183</t>
+          <t>TC_MOB_NAV_028</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.59</v>
+        <v>1.27</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-184</t>
+          <t>TC_MOB_NAV_029</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.48</v>
+        <v>0.87</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-185</t>
+          <t>TC_MOB_NAV_030</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>1.16</v>
+        <v>0.31</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-186</t>
+          <t>TC_MOB_NAV_031</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-187</t>
+          <t>TC_MOB_NAV_032</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-188</t>
+          <t>TC_MOB_NAV_033</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-189</t>
+          <t>TC_MOB_NAV_034</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-190</t>
+          <t>TC_MOB_NAV_035</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.33</v>
+        <v>0.91</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-191</t>
+          <t>TC_MOB_INVAL_001</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-192</t>
+          <t>TC_MOB_INVAL_002</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>1.18</v>
+        <v>0.63</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-193</t>
+          <t>TC_MOB_INVAL_003</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>1.24</v>
+        <v>0.6</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-194</t>
+          <t>TC_MOB_INVAL_004</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-195</t>
+          <t>TC_MOB_INVAL_005</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.53</v>
+        <v>0.84</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-196</t>
+          <t>TC_MOB_INVAL_006</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-197</t>
+          <t>TC_MOB_INVAL_007</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>1.2</v>
+        <v>0.59</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-198</t>
+          <t>TC_MOB_INVAL_008</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-199</t>
+          <t>TC_MOB_INVAL_009</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>1.15</v>
+        <v>0.98</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-200</t>
+          <t>TC_MOB_INVAL_010</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-201</t>
+          <t>TC_MOB_INVAL_011</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-202</t>
+          <t>TC_MOB_INVAL_012</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-203</t>
+          <t>TC_MOB_INVAL_013</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1.36</v>
+        <v>0.49</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-204</t>
+          <t>TC_MOB_INVAL_014</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.29</v>
+        <v>0.73</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-205</t>
+          <t>TC_MOB_INVAL_015</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-206</t>
+          <t>TC_MOB_INVAL_016</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-207</t>
+          <t>TC_MOB_INVAL_017</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-208</t>
+          <t>TC_MOB_INVAL_018</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>1.16</v>
+        <v>0.63</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-209</t>
+          <t>TC_MOB_INVAL_019</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-210</t>
+          <t>TC_MOB_INVAL_020</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-211</t>
+          <t>TC_MOB_INVAL_021</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.41</v>
+        <v>1.22</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-212</t>
+          <t>TC_MOB_INVAL_022</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-213</t>
+          <t>TC_MOB_INVAL_023</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-214</t>
+          <t>TC_MOB_INVAL_024</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-215</t>
+          <t>TC_MOB_INVAL_025</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.02</v>
+        <v>0.87</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-216</t>
+          <t>TC_MOB_INVAL_026</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.76</v>
+        <v>0.35</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-217</t>
+          <t>TC_MOB_INVAL_027</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.95</v>
+        <v>1.38</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-218</t>
+          <t>TC_MOB_INVAL_028</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-219</t>
+          <t>TC_MOB_INVAL_029</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-220</t>
+          <t>TC_MOB_INVAL_030</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>1.06</v>
+        <v>0.25</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-221</t>
+          <t>TC_MOB_INVAL_031</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.41</v>
+        <v>1.13</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-222</t>
+          <t>TC_MOB_INVAL_032</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.28</v>
+        <v>0.9</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-223</t>
+          <t>TC_MOB_INVAL_033</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-224</t>
+          <t>TC_MOB_INVAL_034</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.84</v>
+        <v>1.07</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-225</t>
+          <t>TC_MOB_INVAL_035</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-226</t>
+          <t>TC_MOB_OFFLINE_001</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.59</v>
+        <v>0.9</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-227</t>
+          <t>TC_MOB_OFFLINE_002</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-228</t>
+          <t>TC_MOB_OFFLINE_003</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1.34</v>
+        <v>0.39</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-229</t>
+          <t>TC_MOB_OFFLINE_004</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.65</v>
+        <v>1.32</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-230</t>
+          <t>TC_MOB_OFFLINE_005</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-231</t>
+          <t>TC_MOB_OFFLINE_006</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-232</t>
+          <t>TC_MOB_OFFLINE_007</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-233</t>
+          <t>TC_MOB_OFFLINE_008</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.37</v>
+        <v>1.09</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-234</t>
+          <t>TC_MOB_OFFLINE_009</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1.24</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-235</t>
+          <t>TC_MOB_OFFLINE_010</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-236</t>
+          <t>TC_MOB_OFFLINE_011</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>1.24</v>
+        <v>0.71</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-237</t>
+          <t>TC_MOB_OFFLINE_012</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -10224,7 +10224,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-238</t>
+          <t>TC_MOB_OFFLINE_013</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.5</v>
+        <v>1.34</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-239</t>
+          <t>TC_MOB_OFFLINE_014</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>1.29</v>
+        <v>0.83</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-240</t>
+          <t>TC_MOB_OFFLINE_015</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-241</t>
+          <t>TC_MOB_OFFLINE_016</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.75</v>
+        <v>0.36</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-242</t>
+          <t>TC_MOB_OFFLINE_017</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-243</t>
+          <t>TC_MOB_OFFLINE_018</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1.39</v>
+        <v>0.61</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-244</t>
+          <t>TC_MOB_OFFLINE_019</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.77</v>
+        <v>1.28</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-245</t>
+          <t>TC_MOB_OFFLINE_020</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.35</v>
+        <v>1.11</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-246</t>
+          <t>TC_MOB_OFFLINE_021</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.34</v>
+        <v>0.36</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-247</t>
+          <t>TC_MOB_OFFLINE_022</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-248</t>
+          <t>TC_MOB_OFFLINE_023</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.31</v>
+        <v>1.17</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-249</t>
+          <t>TC_MOB_OFFLINE_024</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-250</t>
+          <t>TC_MOB_OFFLINE_025</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-251</t>
+          <t>TC_MOB_OFFLINE_026</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-252</t>
+          <t>TC_MOB_OFFLINE_027</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-253</t>
+          <t>TC_MOB_OFFLINE_028</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-254</t>
+          <t>TC_MOB_OFFLINE_029</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-255</t>
+          <t>TC_MOB_OFFLINE_030</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.37</v>
+        <v>1.19</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-256</t>
+          <t>TC_MOB_OFFLINE_031</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-257</t>
+          <t>TC_MOB_OFFLINE_032</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-258</t>
+          <t>TC_MOB_OFFLINE_033</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-259</t>
+          <t>TC_MOB_OFFLINE_034</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-260</t>
+          <t>TC_MOB_OFFLINE_035</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-261</t>
+          <t>TC_MOB_MEM_001</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>1.41</v>
+        <v>0.61</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-262</t>
+          <t>TC_MOB_MEM_002</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.8</v>
+        <v>1.43</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-263</t>
+          <t>TC_MOB_MEM_003</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.87</v>
+        <v>0.27</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-264</t>
+          <t>TC_MOB_MEM_004</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.5</v>
+        <v>1.35</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-265</t>
+          <t>TC_MOB_MEM_005</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.86</v>
+        <v>0.49</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-266</t>
+          <t>TC_MOB_MEM_006</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-267</t>
+          <t>TC_MOB_MEM_007</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-268</t>
+          <t>TC_MOB_MEM_008</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>1.24</v>
+        <v>0.83</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-269</t>
+          <t>TC_MOB_MEM_009</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.45</v>
+        <v>1.05</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-270</t>
+          <t>TC_MOB_MEM_010</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-271</t>
+          <t>TC_MOB_MEM_011</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-272</t>
+          <t>TC_MOB_MEM_012</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.98</v>
+        <v>0.35</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-273</t>
+          <t>TC_MOB_MEM_013</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.23</v>
+        <v>0.71</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-274</t>
+          <t>TC_MOB_MEM_014</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-275</t>
+          <t>TC_MOB_MEM_015</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-276</t>
+          <t>TC_MOB_MEM_016</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1.09</v>
+        <v>0.89</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-277</t>
+          <t>TC_MOB_MEM_017</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-278</t>
+          <t>TC_MOB_MEM_018</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-279</t>
+          <t>TC_MOB_MEM_019</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.53</v>
+        <v>1.43</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-280</t>
+          <t>TC_MOB_MEM_020</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>1.29</v>
+        <v>0.82</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-281</t>
+          <t>TC_MOB_MEM_021</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-282</t>
+          <t>TC_MOB_MEM_022</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>1.44</v>
+        <v>0.77</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-283</t>
+          <t>TC_MOB_MEM_023</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1.23</v>
+        <v>0.86</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-284</t>
+          <t>TC_MOB_MEM_024</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-285</t>
+          <t>TC_MOB_MEM_025</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>1.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-286</t>
+          <t>TC_MOB_MEM_026</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.64</v>
+        <v>1.01</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-287</t>
+          <t>TC_MOB_MEM_027</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.88</v>
+        <v>1.07</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-288</t>
+          <t>TC_MOB_MEM_028</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-289</t>
+          <t>TC_MOB_MEM_029</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-290</t>
+          <t>TC_MOB_MEM_030</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-291</t>
+          <t>TC_MOB_MEM_031</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-292</t>
+          <t>TC_MOB_MEM_032</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>1.23</v>
+        <v>0.54</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-293</t>
+          <t>TC_MOB_MEM_033</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.93</v>
+        <v>1.11</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-294</t>
+          <t>TC_MOB_MEM_034</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-295</t>
+          <t>TC_MOB_MEM_035</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>1.21</v>
+        <v>0.53</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-296</t>
+          <t>TC_MOB_MEM_036</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1.24</v>
+        <v>0.33</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-297</t>
+          <t>TC_MOB_MEM_037</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-298</t>
+          <t>TC_MOB_MEM_038</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-299</t>
+          <t>TC_MOB_MEM_039</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.98</v>
+        <v>0.29</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>TC-MOB-300</t>
+          <t>TC_MOB_MEM_040</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.3</v>
+        <v>1.28</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.71</v>
+        <v>0.45</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.62</v>
+        <v>0.36</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.48</v>
+        <v>0.82</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.36</v>
+        <v>0.79</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.48</v>
+        <v>0.85</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.4s without crashing.</t>
+          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.42s without crashing.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.44s without crashing.</t>
+          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.5s without crashing.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.5s without crashing.</t>
+          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.48s without crashing.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.72s without crashing.</t>
+          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.43s without crashing.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.72</v>
+        <v>0.43</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.35s without crashing.</t>
+          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.35</v>
+        <v>0.88</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.36s without crashing.</t>
+          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.5s without crashing.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.68s without crashing.</t>
+          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.36s without crashing.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.62s without crashing.</t>
+          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.55s without crashing.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
+          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.84s without crashing.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.7s without crashing.</t>
+          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.73s without crashing.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.82s without crashing.</t>
+          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.83s without crashing.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.37s without crashing.</t>
+          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.62s without crashing.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.37</v>
+        <v>0.62</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.87s without crashing.</t>
+          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.69s without crashing.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.69s without crashing.</t>
+          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.63s without crashing.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.44s without crashing.</t>
+          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.87s without crashing.</t>
+          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.37s without crashing.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.87</v>
+        <v>0.37</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
+          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.58s without crashing.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.88</v>
+        <v>0.58</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.36s without crashing.</t>
+          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.94s without crashing.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.36</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.86s without crashing.</t>
+          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.39s without crashing.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.86</v>
+        <v>0.39</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.77</v>
+        <v>0.48</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
+          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.73s.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.51s.</t>
+          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.67s.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
+          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.51s.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.57</v>
+        <v>0.37</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.46s.</t>
+          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.81s.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.46</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.62s.</t>
+          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.75s.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
+          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.51s.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.81s.</t>
+          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.74s.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.64s.</t>
+          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.59s.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
+          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.76</v>
+        <v>0.57</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.52s.</t>
+          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.71s.</t>
+          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.43s.</t>
+          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.52s.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.63s.</t>
+          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.66s.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.73s.</t>
+          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.45s.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.73</v>
+        <v>0.45</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.61s.</t>
+          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.32s.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.47s.</t>
+          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.51s.</t>
+          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.61s.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
+          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.73s.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.54s.</t>
+          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.36s.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.54</v>
+        <v>0.36</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
+          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.87s.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1.1</v>
+        <v>0.52</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.84</v>
+        <v>0.46</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.74</v>
+        <v>1.1</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.82s.</t>
+          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
+          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.5s.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.71s.</t>
+          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.77s.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.63s.</t>
+          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.68s.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.48s.</t>
+          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.41s.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.45s.</t>
+          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.1s.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.45</v>
+        <v>1.1</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.94s.</t>
+          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.99s.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
+          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.44s.</t>
+          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.52s.</t>
+          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.78s.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.52</v>
+        <v>0.78</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.43s.</t>
+          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.45s.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
+          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.62s.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.93</v>
+        <v>0.62</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.09s.</t>
+          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.04s.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.83s.</t>
+          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.05s.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.84s.</t>
+          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.53s.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.84</v>
+        <v>0.53</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.78s.</t>
+          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.71s.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.7s.</t>
+          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.69s.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.1s.</t>
+          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.45s.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.66s.</t>
+          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.11s.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.66</v>
+        <v>1.11</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.0s.</t>
+          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.05s.</t>
+          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.7s.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.55s.</t>
+          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.48s.</t>
+          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.4s.</t>
+          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.42s.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.02s.</t>
+          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.83s.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1.02</v>
+        <v>0.83</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
+          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
+          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.76</v>
+        <v>0.53</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
+          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.4s.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.33s.</t>
+          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.47s.</t>
+          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.42s.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.77s.</t>
+          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.64s.</t>
+          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
+          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
+          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.79s.</t>
+          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.42s.</t>
+          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
+          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.51s.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.68s.</t>
+          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.82s.</t>
+          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.65s.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.38s.</t>
+          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.78s.</t>
+          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.78</v>
+        <v>0.32</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.44s.</t>
+          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.84s.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
+          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.68s.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
+          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.79s.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
+          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.82s.</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.35</v>
+        <v>0.82</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.39</v>
+        <v>0.83</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.55s.</t>
+          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.63s.</t>
+          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.63</v>
+        <v>0.39</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.45s.</t>
+          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.53</v>
+        <v>0.83</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.85s.</t>
+          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.85</v>
+        <v>0.32</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.73s.</t>
+          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.51s.</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.75s.</t>
+          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.75</v>
+        <v>0.32</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.64s.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.51s.</t>
+          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.48s.</t>
+          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.66s.</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.48</v>
+        <v>0.66</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
+          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.62s.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.42s.</t>
+          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.58s.</t>
+          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.35s.</t>
+          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.35</v>
+        <v>0.67</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.35s.</t>
+          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
+          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.4s.</t>
+          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.61s.</t>
+          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
+          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.71s.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.39</v>
+        <v>0.71</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
+          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.75s.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
+          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.42s.</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.51s.</t>
+          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.55s.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.45s.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
+          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.77</v>
+        <v>0.44</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.48s.</t>
+          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
+          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.78</v>
+        <v>0.52</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.66</v>
+        <v>1.13</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.82s.</t>
+          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.85s.</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
+          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.48s.</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.85s.</t>
+          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.05s.</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.47s.</t>
+          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.45s.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.62s.</t>
+          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.68s.</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.15s.</t>
+          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.51s.</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>1.15</v>
+        <v>0.51</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.96s.</t>
+          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.69s.</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.9s.</t>
+          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.42s.</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.9</v>
+        <v>0.42</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.5s.</t>
+          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.24s.</t>
+          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.46s.</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.24</v>
+        <v>0.46</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.79s.</t>
+          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.42s.</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.79</v>
+        <v>0.42</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
+          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.09s.</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.71</v>
+        <v>1.09</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.49s.</t>
+          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.24s.</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.49</v>
+        <v>1.24</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.13s.</t>
+          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>1.13</v>
+        <v>0.93</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
+          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.84s.</t>
+          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.07s.</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.84</v>
+        <v>1.07</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.45s.</t>
+          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.98s.</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.7s.</t>
+          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.67s.</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.2s.</t>
+          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.98s.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.48s.</t>
+          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.21s.</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.48</v>
+        <v>1.21</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.24s.</t>
+          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.84s.</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.97s.</t>
+          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.89s.</t>
+          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.08s.</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.89</v>
+        <v>1.08</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.89s.</t>
+          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.68s.</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.08s.</t>
+          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.06s.</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.14s.</t>
+          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.77s.</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1.14</v>
+        <v>0.77</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.07s.</t>
+          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.12s.</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.16s.</t>
+          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.52s.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1.16</v>
+        <v>0.52</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.29</v>
+        <v>0.51</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
+          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
+          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.31</v>
+        <v>0.54</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.62s.</t>
+          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.62</v>
+        <v>0.3</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
+          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.73s.</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
+          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.72s.</t>
+          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.59s.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.66s.</t>
+          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.46s.</t>
+          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.43s.</t>
+          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.66s.</t>
+          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.46s.</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
+          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.74s.</t>
+          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
+          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.67</v>
+        <v>0.45</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.75s.</t>
+          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.39s.</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.28s.</t>
+          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.26s.</t>
+          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.26</v>
+        <v>0.65</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
+          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
+          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.64</v>
+        <v>0.27</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
+          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.29s.</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.52</v>
+        <v>0.29</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
+          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.36s.</t>
+          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
+          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
+          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
+          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.72s.</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.32</v>
+        <v>0.72</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.36s.</t>
+          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.49s.</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.33s.</t>
+          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.34s.</t>
+          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.34</v>
+        <v>0.67</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.7s.</t>
+          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
+          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.35s.</t>
+          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.22</v>
+        <v>0.48</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.65s.</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.27</v>
+        <v>0.65</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
+          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
+          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.52</v>
+        <v>0.27</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
+          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
+          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
+          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.5s.</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.37s.</t>
+          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
+          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.37s.</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.58</v>
+        <v>0.37</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
+          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.53</v>
+        <v>0.31</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
+          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.47s.</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
+          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.34s.</t>
+          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.63s.</t>
+          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
+          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
+          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
+          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.65s.</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
+          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
+          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
+          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.47s.</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.37s.</t>
+          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.24s.</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.45</v>
+        <v>0.24</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.22s.</t>
+          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.22</v>
+        <v>0.64</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
+          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.32s.</t>
+          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.65s.</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
+          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
+          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.26s.</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.59</v>
+        <v>0.26</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.34s.</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
+          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.29s.</t>
+          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.41</v>
+        <v>0.62</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.38</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.52</v>
+        <v>0.37</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.42s without crashing.</t>
+          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.63s without crashing.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.5s without crashing.</t>
+          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.47s without crashing.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.48s without crashing.</t>
+          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.91s without crashing.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.43s without crashing.</t>
+          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.55s without crashing.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
+          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.5s without crashing.</t>
+          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.77s without crashing.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.36s without crashing.</t>
+          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.43s without crashing.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.55s without crashing.</t>
+          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.52s without crashing.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.84s without crashing.</t>
+          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.51s without crashing.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.84</v>
+        <v>0.51</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.73s without crashing.</t>
+          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.52s without crashing.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.83s without crashing.</t>
+          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.42s without crashing.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.62s without crashing.</t>
+          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.84s without crashing.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.69s without crashing.</t>
+          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.7s without crashing.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.63s without crashing.</t>
+          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.92s without crashing.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.63</v>
+        <v>0.92</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.49s without crashing.</t>
+          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.46s without crashing.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
+          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.87s without crashing.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.37s without crashing.</t>
+          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.72s without crashing.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.37</v>
+        <v>0.72</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.58s without crashing.</t>
+          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.85s without crashing.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.94s without crashing.</t>
+          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.54s without crashing.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.39s without crashing.</t>
+          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.7s without crashing.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.37</v>
+        <v>0.88</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.63</v>
+        <v>0.37</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.54</v>
+        <v>0.82</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.33</v>
+        <v>0.49</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.73s.</t>
+          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.46s.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.67s.</t>
+          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.42s.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.51s.</t>
+          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.36s.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
+          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.83s.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.37</v>
+        <v>0.83</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.81s.</t>
+          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.72s.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.75s.</t>
+          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.75</v>
+        <v>0.37</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.51s.</t>
+          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.45s.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.66s.</t>
+          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
+          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
+          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.82s.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.74s.</t>
+          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.71s.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.59s.</t>
+          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.74s.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
+          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.55s.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
+          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.4s.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.52s.</t>
+          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.39s.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.66s.</t>
+          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.82s.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.45s.</t>
+          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.32s.</t>
+          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.72s.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.32</v>
+        <v>0.72</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
+          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.37</v>
+        <v>0.57</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.61s.</t>
+          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.73s.</t>
+          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.32s.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.36s.</t>
+          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.42s.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
+          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.87s.</t>
+          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.98</v>
+        <v>0.58</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.61</v>
+        <v>0.89</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1.1</v>
+        <v>0.91</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
+          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.9s.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.5s.</t>
+          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.47s.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.77s.</t>
+          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.77</v>
+        <v>0.97</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.68s.</t>
+          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.62s.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.41s.</t>
+          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.94s.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.1s.</t>
+          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.88s.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.99s.</t>
+          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
+          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
+          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.07s.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.78s.</t>
+          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.84s.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.45s.</t>
+          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.45</v>
+        <v>0.87</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.62s.</t>
+          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.88s.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.62</v>
+        <v>0.88</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.04s.</t>
+          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.05s.</t>
+          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.53s.</t>
+          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.51s.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.71s.</t>
+          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.1s.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.69s.</t>
+          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.82s.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.45s.</t>
+          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.45</v>
+        <v>0.86</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.11s.</t>
+          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.02s.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
+          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.7s.</t>
+          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.72s.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
+          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
+          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.08s.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.42s.</t>
+          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.42</v>
+        <v>0.87</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.83s.</t>
+          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.89s.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.34</v>
+        <v>0.79</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
+          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.38s.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.4s.</t>
+          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.85s.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
+          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.42s.</t>
+          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
+          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.44s.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
+          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
+          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.41s.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
+          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
+          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.74s.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.51s.</t>
+          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.55s.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
+          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.65s.</t>
+          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.59s.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.65s.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
+          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.84s.</t>
+          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.57s.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.84</v>
+        <v>0.57</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.68s.</t>
+          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.73s.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.79s.</t>
+          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.41s.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.79</v>
+        <v>0.41</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
+          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.82s.</t>
+          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.64s.</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
+          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.78s.</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
+          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
+          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.54s.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.32</v>
+        <v>0.54</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
+          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.61s.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
+          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.79s.</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.51s.</t>
+          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.44s.</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
+          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.78s.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.32</v>
+        <v>0.78</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.64s.</t>
+          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
+          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.74s.</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.66s.</t>
+          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
+          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.62s.</t>
+          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.68s.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
+          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
+          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.73</v>
+        <v>0.28</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
+          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.67</v>
+        <v>0.31</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
+          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.61s.</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.53s.</t>
+          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
+          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
+          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
+          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
+          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.46s.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
+          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.7s.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.71s.</t>
+          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.32s.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.71</v>
+        <v>0.32</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
+          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.45s.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.78</v>
+        <v>0.45</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.75s.</t>
+          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
+          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.42s.</t>
+          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.53s.</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
+          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.65s.</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.34</v>
+        <v>0.65</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.55s.</t>
+          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.45s.</t>
+          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
+          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
+          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
+          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
+          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
+          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.68s.</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.88</v>
+        <v>1.16</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.5</v>
+        <v>1.12</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.13</v>
+        <v>0.89</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.85s.</t>
+          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.95s.</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.48s.</t>
+          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.43s.</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.05s.</t>
+          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.92s.</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.45s.</t>
+          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.7s.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.68s.</t>
+          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.02s.</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.68</v>
+        <v>1.02</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.51s.</t>
+          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.45s.</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.69s.</t>
+          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.42s.</t>
+          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.19s.</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.42</v>
+        <v>1.19</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
+          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.73s.</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.46s.</t>
+          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.25s.</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.46</v>
+        <v>1.25</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.42s.</t>
+          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.01s.</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.42</v>
+        <v>1.01</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.09s.</t>
+          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1.09</v>
+        <v>0.63</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.24s.</t>
+          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.77s.</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.24</v>
+        <v>0.77</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
+          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.97s.</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
+          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.25s.</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.63</v>
+        <v>1.25</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.07s.</t>
+          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.07</v>
+        <v>0.38</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.98s.</t>
+          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.74s.</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.98</v>
+        <v>0.74</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.67s.</t>
+          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.98s.</t>
+          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.17s.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.98</v>
+        <v>1.17</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.21s.</t>
+          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.06s.</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.84s.</t>
+          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.15s.</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
+          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.08s.</t>
+          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.72s.</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>1.08</v>
+        <v>0.72</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.68s.</t>
+          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.97s.</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.06s.</t>
+          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.77s.</t>
+          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.12s.</t>
+          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.72s.</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>1.12</v>
+        <v>0.72</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.52s.</t>
+          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.51</v>
+        <v>0.38</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.52</v>
+        <v>0.37</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
+          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.73s.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
+          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
+          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.73s.</t>
+          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.39s.</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.59s.</t>
+          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
+          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
+          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.42s.</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.46s.</t>
+          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
+          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.26s.</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
+          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.39s.</t>
+          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
+          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
+          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
+          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.26s.</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.29s.</t>
+          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.43s.</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.41</v>
+        <v>0.67</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.66s.</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.27</v>
+        <v>0.66</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
+          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.28s.</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.54</v>
+        <v>0.28</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
+          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
+          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.72s.</t>
+          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.49s.</t>
+          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
+          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.59s.</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
+          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.36s.</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.67</v>
+        <v>0.36</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
+          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
+          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.36s.</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
+          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.65s.</t>
+          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.57s.</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
+          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
+          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.32s.</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
+          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.5s.</t>
+          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
+          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.24s.</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
+          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.37s.</t>
+          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.43s.</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
+          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.47s.</t>
+          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
+          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
+          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.57s.</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
+          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
+          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.33</v>
+        <v>0.49</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
+          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.65s.</t>
+          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.64</v>
+        <v>0.44</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.47s.</t>
+          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
+          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.54s.</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.24s.</t>
+          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
+          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.65s.</t>
+          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
+          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.43s.</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.26s.</t>
+          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.43s.</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.34s.</t>
+          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.26s.</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
+          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
+          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.4s.</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.42</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.37</v>
+        <v>0.71</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.82</v>
+        <v>0.37</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.63s without crashing.</t>
+          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.72s without crashing.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.47s without crashing.</t>
+          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.64s without crashing.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.91s without crashing.</t>
+          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.68s without crashing.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.55s without crashing.</t>
+          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
+          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.83s without crashing.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.77s without crashing.</t>
+          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.94s without crashing.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.43s without crashing.</t>
+          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.37s without crashing.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.52s without crashing.</t>
+          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.73s without crashing.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.51s without crashing.</t>
+          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.75s without crashing.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.52s without crashing.</t>
+          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.35s without crashing.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.42s without crashing.</t>
+          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.57s without crashing.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.42</v>
+        <v>0.57</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.84s without crashing.</t>
+          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.8s without crashing.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.7s without crashing.</t>
+          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.84s without crashing.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.92s without crashing.</t>
+          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.56s without crashing.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.46s without crashing.</t>
+          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.94s without crashing.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.87s without crashing.</t>
+          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.73s without crashing.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.72s without crashing.</t>
+          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.47s without crashing.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.72</v>
+        <v>0.47</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.85s without crashing.</t>
+          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.54s without crashing.</t>
+          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.8s without crashing.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.7s without crashing.</t>
+          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.4s without crashing.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.88</v>
+        <v>0.39</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.46</v>
+        <v>0.88</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.82</v>
+        <v>0.45</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.33</v>
+        <v>0.68</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.85</v>
+        <v>0.42</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.46s.</t>
+          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.42s.</t>
+          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.36s.</t>
+          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.83s.</t>
+          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.65s.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.72s.</t>
+          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
+          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.36s.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.45s.</t>
+          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.8s.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
+          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.77s.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
+          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.49</v>
+        <v>0.37</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.82s.</t>
+          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.71s.</t>
+          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
+          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.82s.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.74s.</t>
+          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.77s.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.55s.</t>
+          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.53s.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.4s.</t>
+          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.73s.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.39s.</t>
+          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.69s.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.82s.</t>
+          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.71s.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
+          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.69s.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.72s.</t>
+          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.39s.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.57</v>
+        <v>0.39</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
+          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.32s.</t>
+          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.87s.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.32</v>
+        <v>0.87</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.42s.</t>
+          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.69s.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
+          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.7s.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
+          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.44s.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.84</v>
+        <v>0.44</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.98</v>
+        <v>1.1</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.53</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.93</v>
+        <v>0.46</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.11</v>
+        <v>0.59</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.89</v>
+        <v>0.6</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.9s.</t>
+          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.47s.</t>
+          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.89s.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
+          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.43s.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.62s.</t>
+          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.4s.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.94s.</t>
+          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.42s.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.88s.</t>
+          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.46s.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.88</v>
+        <v>0.46</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
+          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.46s.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.93</v>
+        <v>0.46</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
+          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.4s.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.97</v>
+        <v>0.4</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.07s.</t>
+          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1.07</v>
+        <v>0.6</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.84s.</t>
+          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.02s.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
+          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.88s.</t>
+          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.39s.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.88</v>
+        <v>0.39</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
+          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
+          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.51s.</t>
+          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.8s.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.1s.</t>
+          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.09s.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.82s.</t>
+          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.99s.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
+          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.47s.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.02s.</t>
+          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.91s.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
+          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.72s.</t>
+          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.72</v>
+        <v>0.97</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
+          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.84s.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.08s.</t>
+          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.44s.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>1.08</v>
+        <v>0.44</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
+          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.01s.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.89s.</t>
+          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.65s.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.89</v>
+        <v>0.65</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.38</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.62</v>
+        <v>0.36</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.38s.</t>
+          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.85s.</t>
+          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.85</v>
+        <v>0.58</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
+          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.59s.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
+          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.4s.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.44s.</t>
+          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.4s.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
+          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.41s.</t>
+          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.57s.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.41</v>
+        <v>0.57</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
+          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.46</v>
+        <v>0.83</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.74s.</t>
+          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.5s.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
+          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.34s.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
+          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.55s.</t>
+          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.82s.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.39</v>
+        <v>0.82</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.59s.</t>
+          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.7s.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.65s.</t>
+          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
+          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.57s.</t>
+          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.75s.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.73s.</t>
+          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.57s.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.41s.</t>
+          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
+          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.51s.</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.64s.</t>
+          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.31s.</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.78s.</t>
+          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.45s.</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.78</v>
+        <v>0.45</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
+          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
+          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.54s.</t>
+          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.8s.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.61s.</t>
+          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.79s.</t>
+          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.81s.</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.44s.</t>
+          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.78s.</t>
+          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.78</v>
+        <v>0.48</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.36s.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.74s.</t>
+          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
+          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.46s.</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
+          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.68s.</t>
+          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
+          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
+          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.35s.</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
+          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
+          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.31</v>
+        <v>0.59</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.61s.</t>
+          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
+          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.34</v>
+        <v>0.77</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
+          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.78</v>
+        <v>0.34</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
+          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.75s.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.46s.</t>
+          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.7s.</t>
+          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.61s.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.32s.</t>
+          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.45s.</t>
+          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
+          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.37s.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.73</v>
+        <v>0.37</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.53s.</t>
+          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.53</v>
+        <v>0.31</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.65s.</t>
+          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.65</v>
+        <v>0.41</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
+          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.72s.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
+          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.51s.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
+          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
+          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.62s.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
+          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.68s.</t>
+          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.61s.</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>1.12</v>
+        <v>0.58</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.95s.</t>
+          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.48s.</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.95</v>
+        <v>0.48</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.43s.</t>
+          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.69s.</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.92s.</t>
+          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.2s.</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.7s.</t>
+          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.96s.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.45s.</t>
+          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.45</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
+          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.89s.</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.19s.</t>
+          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.37s.</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>1.19</v>
+        <v>0.37</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.73s.</t>
+          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.85s.</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.25s.</t>
+          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.96s.</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.01s.</t>
+          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.17s.</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
+          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.97s.</t>
+          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.64s.</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.97</v>
+        <v>0.64</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.25s.</t>
+          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.25</v>
+        <v>0.38</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
+          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.08s.</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.38</v>
+        <v>1.08</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.74s.</t>
+          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.74</v>
+        <v>0.38</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
+          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.36s.</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.17s.</t>
+          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.69s.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.06s.</t>
+          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.62s.</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>1.06</v>
+        <v>0.62</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.15s.</t>
+          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>1.15</v>
+        <v>0.93</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
+          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.67s.</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.72s.</t>
+          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.99s.</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.97s.</t>
+          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.43s.</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
+          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.66s.</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
+          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.22s.</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.72s.</t>
+          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
+          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.37</v>
+        <v>0.65</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.73s.</t>
+          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.73</v>
+        <v>0.5</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.72s.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.41</v>
+        <v>0.72</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
+          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.39s.</t>
+          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
+          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.7s.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.27</v>
+        <v>0.7</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
+          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.42s.</t>
+          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.57s.</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.42</v>
+        <v>0.57</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
+          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.57s.</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
+          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.32</v>
+        <v>0.55</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.73s.</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.26s.</t>
+          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.33s.</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
+          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
+          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.39s.</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.65</v>
+        <v>0.39</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
+          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.37s.</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.65</v>
+        <v>0.37</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
+          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
+          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.26s.</t>
+          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.43s.</t>
+          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
+          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.66s.</t>
+          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.28s.</t>
+          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
+          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
+          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.35s.</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
+          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.59s.</t>
+          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.28s.</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.36s.</t>
+          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
+          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.33s.</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.48</v>
+        <v>0.33</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.36s.</t>
+          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
+          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.7s.</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.57s.</t>
+          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.55s.</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
+          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.28</v>
+        <v>0.51</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.32s.</t>
+          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
+          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.36s.</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
+          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.24s.</t>
+          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.55s.</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.43s.</t>
+          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.22s.</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
+          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
+          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
+          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.57s.</t>
+          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
+          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
+          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
+          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.49</v>
+        <v>0.64</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
+          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
+          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
+          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.44</v>
+        <v>0.61</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
+          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.4s.</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
+          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.54s.</t>
+          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.36s.</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
+          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.67s.</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.43s.</t>
+          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.43s.</t>
+          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.26s.</t>
+          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.54s.</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.26</v>
+        <v>0.54</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
+          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.26s.</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.4s.</t>
+          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.64</v>
+        <v>0.44</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.53</v>
+        <v>0.82</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.37</v>
+        <v>0.84</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.72s without crashing.</t>
+          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.86s without crashing.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.64s without crashing.</t>
+          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.42s without crashing.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.68s without crashing.</t>
+          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.5s without crashing.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
+          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.65s without crashing.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.83s without crashing.</t>
+          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.68s without crashing.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.94s without crashing.</t>
+          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.47s without crashing.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.37s without crashing.</t>
+          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.37</v>
+        <v>0.88</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.73s without crashing.</t>
+          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.54s without crashing.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.75s without crashing.</t>
+          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.86s without crashing.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.35s without crashing.</t>
+          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.7s without crashing.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.57s without crashing.</t>
+          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.57</v>
+        <v>0.76</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.8s without crashing.</t>
+          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.68s without crashing.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.84s without crashing.</t>
+          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.56s without crashing.</t>
+          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.89s without crashing.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.94s without crashing.</t>
+          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.87s without crashing.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.73s without crashing.</t>
+          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.81s without crashing.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.47s without crashing.</t>
+          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.67s without crashing.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
+          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.8s without crashing.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.8s without crashing.</t>
+          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.53s without crashing.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.4s without crashing.</t>
+          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.91s without crashing.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.4</v>
+        <v>0.91</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.39</v>
+        <v>0.74</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.71</v>
+        <v>0.48</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
+          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.74s.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
+          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
+          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.64s.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.65s.</t>
+          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.45s.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
+          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.36s.</t>
+          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.64s.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.8s.</t>
+          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.64s.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.77s.</t>
+          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.77</v>
+        <v>0.49</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
+          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.54s.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.37</v>
+        <v>0.54</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
+          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.52s.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
+          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.82s.</t>
+          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.82</v>
+        <v>0.35</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.77s.</t>
+          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.38s.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.77</v>
+        <v>0.38</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.53s.</t>
+          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.56s.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.73s.</t>
+          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.73</v>
+        <v>0.48</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.69s.</t>
+          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.78s.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.71s.</t>
+          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.44s.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.69s.</t>
+          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
+          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.52s.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.79</v>
+        <v>0.52</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.39s.</t>
+          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
+          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.87s.</t>
+          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.69s.</t>
+          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.7s.</t>
+          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.7</v>
+        <v>0.37</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.44s.</t>
+          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.59</v>
+        <v>0.39</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
+          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.5s.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.89s.</t>
+          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.96s.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.43s.</t>
+          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.77s.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.4s.</t>
+          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.63s.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.42s.</t>
+          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.51s.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.46s.</t>
+          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.42s.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.46s.</t>
+          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.46</v>
+        <v>0.93</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.4s.</t>
+          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.71s.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
+          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.02s.</t>
+          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.05s.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
+          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.64s.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.39s.</t>
+          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.8s.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.39</v>
+        <v>0.8</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.6s.</t>
+          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.52s.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
+          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.12s.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.97</v>
+        <v>1.12</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.8s.</t>
+          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.78s.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.09s.</t>
+          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.54s.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.99s.</t>
+          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.55s.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.99</v>
+        <v>0.55</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.47s.</t>
+          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.4s.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.91s.</t>
+          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.38s.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.91</v>
+        <v>0.38</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
+          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.67s.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.97s.</t>
+          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.66s.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.84s.</t>
+          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.11s.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.84</v>
+        <v>1.11</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.44s.</t>
+          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.01s.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.44</v>
+        <v>1.01</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.01s.</t>
+          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.54s.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.01</v>
+        <v>0.54</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.65s.</t>
+          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.65</v>
+        <v>1.06</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
+          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
+          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.55s.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
+          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.65s.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.59s.</t>
+          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.49s.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.59</v>
+        <v>0.49</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.4s.</t>
+          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.4s.</t>
+          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.72s.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
+          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.61s.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.57s.</t>
+          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
+          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.5s.</t>
+          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.7s.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.34s.</t>
+          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.42s.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
+          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.31s.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
+          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.82s.</t>
+          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.81s.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.7s.</t>
+          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.45s.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
+          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
+          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.75s.</t>
+          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
+          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.51s.</t>
+          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.51</v>
+        <v>0.35</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.31s.</t>
+          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.45s.</t>
+          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
+          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.73s.</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
+          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.49s.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.8s.</t>
+          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.81s.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
+          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.3s.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.67</v>
+        <v>0.3</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.81s.</t>
+          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.7s.</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
+          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.36s.</t>
+          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
+          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.46s.</t>
+          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
+          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
+          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.7s.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.35s.</t>
+          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.76s.</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.35</v>
+        <v>0.76</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
+          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
+          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
+          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.72s.</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.5s.</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
+          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
+          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.75s.</t>
+          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.33s.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
+          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.42s.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.61s.</t>
+          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.51s.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
+          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
+          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.37s.</t>
+          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
+          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.33s.</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
+          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.74s.</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.41</v>
+        <v>0.74</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.72s.</t>
+          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.71s.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.51s.</t>
+          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.78s.</t>
+          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.36s.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.78</v>
+        <v>0.36</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
+          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.62s.</t>
+          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.62</v>
+        <v>0.28</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
+          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.41</v>
+        <v>0.77</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.47s.</t>
+          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.66s.</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.61s.</t>
+          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>1.06</v>
+        <v>0.64</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.48s.</t>
+          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.09s.</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.48</v>
+        <v>1.09</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.69s.</t>
+          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.0s.</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.2s.</t>
+          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.61s.</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.2</v>
+        <v>0.61</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.96s.</t>
+          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.47s.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.96</v>
+        <v>0.47</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.02s.</t>
+          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.7s.</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>1.02</v>
+        <v>0.7</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
+          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.89s.</t>
+          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.68s.</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.37s.</t>
+          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.91s.</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.37</v>
+        <v>0.91</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.85s.</t>
+          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.1s.</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.96s.</t>
+          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.02s.</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.17s.</t>
+          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.51s.</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>1.17</v>
+        <v>0.51</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
+          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.1s.</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.77s.</t>
+          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.64s.</t>
+          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.0s.</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
+          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.07s.</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.38</v>
+        <v>1.07</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.08s.</t>
+          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
+          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.62s.</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.36s.</t>
+          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.07s.</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.36</v>
+        <v>1.07</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.69s.</t>
+          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.62s.</t>
+          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.42s.</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.62</v>
+        <v>0.42</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
+          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.44s.</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.93</v>
+        <v>0.44</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.67s.</t>
+          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.43s.</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.99s.</t>
+          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.43s.</t>
+          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.66s.</t>
+          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.56s.</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.22s.</t>
+          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.56s.</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
+          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.85s.</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
+          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.09s.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.59</v>
+        <v>1.09</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.65</v>
+        <v>0.28</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.29</v>
+        <v>0.57</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
+          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.72s.</t>
+          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.49s.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
+          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
+          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
+          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.7s.</t>
+          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.65s.</t>
+          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.57s.</t>
+          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.57</v>
+        <v>0.47</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.57s.</t>
+          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
+          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.55</v>
+        <v>0.27</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.73s.</t>
+          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.57s.</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.33s.</t>
+          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.39s.</t>
+          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.37s.</t>
+          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.49s.</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
+          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
+          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.56s.</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
+          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.62s.</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
+          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.25s.</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
+          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.66s.</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
+          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
+          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
+          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.35s.</t>
+          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
+          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
+          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.28s.</t>
+          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.29s.</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
+          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.33s.</t>
+          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
+          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.31</v>
+        <v>0.54</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.7s.</t>
+          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.34s.</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.59</v>
+        <v>0.35</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
+          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
+          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
+          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.36s.</t>
+          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
+          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.55s.</t>
+          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
+          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.22s.</t>
+          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.56s.</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
+          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.46</v>
+        <v>0.35</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
+          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
+          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
+          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.67s.</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
+          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
+          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
+          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
+          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
+          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.61</v>
+        <v>0.44</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.4s.</t>
+          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
+          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.67s.</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.36s.</t>
+          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.57s.</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
+          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.34s.</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
+          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.47s.</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.67s.</t>
+          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
+          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.54s.</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.28</v>
+        <v>0.54</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
+          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.54s.</t>
+          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.26s.</t>
+          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.37s.</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.36</v>
+        <v>0.84</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.7</v>
+        <v>0.48</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.82</v>
+        <v>0.39</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.86s without crashing.</t>
+          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.81s without crashing.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.42s without crashing.</t>
+          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.55s without crashing.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.5s without crashing.</t>
+          <t>User taps Auth action button #3 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.65s without crashing.</t>
+          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.83s without crashing.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.68s without crashing.</t>
+          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.72s without crashing.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.47s without crashing.</t>
+          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.89s without crashing.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.88s without crashing.</t>
+          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.77s without crashing.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.54s without crashing.</t>
+          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.54</v>
+        <v>0.78</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.86s without crashing.</t>
+          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.7s without crashing.</t>
+          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.82s without crashing.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
+          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.9s without crashing.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.68s without crashing.</t>
+          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
+          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.65s without crashing.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.89s without crashing.</t>
+          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.59s without crashing.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.87s without crashing.</t>
+          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.48s without crashing.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.87</v>
+        <v>0.48</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.81s without crashing.</t>
+          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.43s without crashing.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.67s without crashing.</t>
+          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.54s without crashing.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.8s without crashing.</t>
+          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.6s without crashing.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.53s without crashing.</t>
+          <t>User taps Auth action button #19 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.81s without crashing.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.91s without crashing.</t>
+          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.46s without crashing.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.91</v>
+        <v>0.46</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.48</v>
+        <v>0.85</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.74s.</t>
+          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.54s.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.64s.</t>
+          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.45s.</t>
+          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.8s.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
+          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.64s.</t>
+          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.32s.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.64s.</t>
+          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
+          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.46s.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.54s.</t>
+          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.52s.</t>
+          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.7s.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
+          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
+          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.43s.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.38s.</t>
+          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.75s.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.56s.</t>
+          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.78s.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.78s.</t>
+          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.78</v>
+        <v>0.57</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.44s.</t>
+          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.39s.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
+          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.35</v>
+        <v>0.86</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.52s.</t>
+          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.38s.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
+          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.42s.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.6s.</t>
+          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.63s.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
+          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.85s.</t>
+          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
+          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.43s.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.35s.</t>
+          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.66</v>
+        <v>1.12</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1.11</v>
+        <v>0.68</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.53</v>
+        <v>0.86</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.39</v>
+        <v>0.98</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.5s.</t>
+          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.5</v>
+        <v>1.06</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.96s.</t>
+          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.83s.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.96</v>
+        <v>0.83</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.77s.</t>
+          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.47s.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.63s.</t>
+          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.83s.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.63</v>
+        <v>0.83</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.51s.</t>
+          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.48s.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.42s.</t>
+          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.65s.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
+          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.55s.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.71s.</t>
+          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.96s.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
+          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.63s.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.87</v>
+        <v>0.63</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.05s.</t>
+          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.92s.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.64s.</t>
+          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.8s.</t>
+          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.52s.</t>
+          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.65s.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.12s.</t>
+          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.08s.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.78s.</t>
+          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.38s.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.78</v>
+        <v>0.38</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.54s.</t>
+          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.63s.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.55s.</t>
+          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.95s.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.4s.</t>
+          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.68s.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.38s.</t>
+          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.95s.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.38</v>
+        <v>0.95</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.67s.</t>
+          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.58s.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.66s.</t>
+          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.98s.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.11s.</t>
+          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.51s.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.01s.</t>
+          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.45s.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.54s.</t>
+          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.54</v>
+        <v>0.86</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
+          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.8</v>
+        <v>0.38</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.74</v>
+        <v>0.44</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.37</v>
+        <v>0.77</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
+          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.5s.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.55s.</t>
+          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.65s.</t>
+          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.47s.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.49s.</t>
+          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.37s.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.49</v>
+        <v>0.37</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
+          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.36</v>
+        <v>0.66</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.72s.</t>
+          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.47s.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.72</v>
+        <v>0.47</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.61s.</t>
+          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.64s.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
+          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.54s.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
+          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.76</v>
+        <v>0.53</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.7s.</t>
+          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.42s.</t>
+          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.31s.</t>
+          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
+          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.77s.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.81s.</t>
+          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.61s.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.45s.</t>
+          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
+          <t>User taps Registry interactive card/button #16 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.56s.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.33s.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.57s.</t>
+          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.84s.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.57</v>
+        <v>0.84</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
+          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.66</v>
+        <v>0.48</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
+          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.74s.</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.53</v>
+        <v>0.74</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.67s.</t>
+          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.74s.</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.73s.</t>
+          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.49s.</t>
+          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.81s.</t>
+          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.43s.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.3s.</t>
+          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.8s.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.7s.</t>
+          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.7</v>
+        <v>0.39</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.69s.</t>
+          <t>User taps Registry interactive card/button #29 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.64s.</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
+          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.62</v>
+        <v>0.29</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
+          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
+          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.32s.</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
+          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
+          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.68s.</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.52</v>
+        <v>0.68</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
+          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.65s.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.7s.</t>
+          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.76s.</t>
+          <t>User taps Network diagnostic button #7 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.48s.</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.76</v>
+        <v>0.48</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
+          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.38</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
+          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.72s.</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.72s.</t>
+          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.5s.</t>
+          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.29s.</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
+          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
+          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.33s.</t>
+          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.42s.</t>
+          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.29s.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.42</v>
+        <v>0.29</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.51s.</t>
+          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
+          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
+          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.4s.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
+          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.35s.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
+          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.33s.</t>
+          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.74s.</t>
+          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.74</v>
+        <v>0.44</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.71s.</t>
+          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.55s.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.59s.</t>
+          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.48s.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.36s.</t>
+          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.52s.</t>
+          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.52</v>
+        <v>0.31</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
+          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.77s.</t>
+          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.77</v>
+        <v>0.3</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.66s.</t>
+          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.45s.</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
+          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.36s.</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.67</v>
+        <v>1.02</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.78</v>
+        <v>0.52</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.09s.</t>
+          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.22s.</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.0s.</t>
+          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.61s.</t>
+          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.47s.</t>
+          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.7s.</t>
+          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.0s.</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
+          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.24s.</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.38</v>
+        <v>1.24</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.68s.</t>
+          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.4s.</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.91s.</t>
+          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.06s.</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.1s.</t>
+          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.18s.</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.02s.</t>
+          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.91s.</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.51s.</t>
+          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.12s.</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.51</v>
+        <v>1.12</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.1s.</t>
+          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
+          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.6s.</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.0s.</t>
+          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.92s.</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.07s.</t>
+          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.02s.</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
+          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.03</v>
+        <v>0.63</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.62s.</t>
+          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.05s.</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.62</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.07s.</t>
+          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.74s.</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>1.07</v>
+        <v>0.74</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
+          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.13s.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.42s.</t>
+          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.13s.</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.42</v>
+        <v>1.13</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.44s.</t>
+          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.91s.</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.44</v>
+        <v>0.91</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.43s.</t>
+          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.54s.</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.94s.</t>
+          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.56s.</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
+          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.51s.</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.56s.</t>
+          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.56s.</t>
+          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.85s.</t>
+          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.13s.</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.85</v>
+        <v>1.13</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.09s.</t>
+          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.81s.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
+          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.49s.</t>
+          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
+          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.56s.</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
+          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.42s.</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
+          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
+          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
+          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.4s.</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.3s.</t>
+          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.59s.</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.27</v>
+        <v>0.59</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.57s.</t>
+          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
+          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.26s.</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
+          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.68s.</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.49s.</t>
+          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
+          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.46s.</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.56s.</t>
+          <t>User executes offline storage operation #17 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.62s.</t>
+          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.6s.</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.25s.</t>
+          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.66s.</t>
+          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
+          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
+          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
+          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
+          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
+          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
+          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.63</v>
+        <v>0.44</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.29s.</t>
+          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.43s.</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
+          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.54s.</t>
+          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.34s.</t>
+          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.55s.</t>
+          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
+          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.55s.</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
+          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.52</v>
+        <v>0.3</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
+          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
+          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
+          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.33</v>
+        <v>0.62</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
+          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
+          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.56s.</t>
+          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.32s.</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.67s.</t>
+          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.28s.</t>
+          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.28</v>
+        <v>0.52</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
+          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
+          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.29s.</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
+          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
+          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.36s.</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
+          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.34s.</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.31s.</t>
+          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.27</v>
+        <v>0.59</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.67s.</t>
+          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.67</v>
+        <v>0.27</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.57s.</t>
+          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.63s.</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.34s.</t>
+          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.47s.</t>
+          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
+          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.54s.</t>
+          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.29s.</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
+          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.37s.</t>
+          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.23s.</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
+          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.68s.</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Mobile_Application_Appium_Test_Report.xlsx
+++ b/reports/Mobile_Application_Appium_Test_Report.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.89</v>
+        <v>0.38</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.88</v>
+        <v>0.49</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.81s without crashing.</t>
+          <t>User taps Auth action button #1 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.6s without crashing.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.55s without crashing.</t>
+          <t>User taps Auth action button #2 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.58s without crashing.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.83s without crashing.</t>
+          <t>User taps Auth action button #4 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.37s without crashing.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.83</v>
+        <v>0.37</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.72s without crashing.</t>
+          <t>User taps Auth action button #5 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.9s without crashing.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.89s without crashing.</t>
+          <t>User taps Auth action button #6 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.77s without crashing.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.77s without crashing.</t>
+          <t>User taps Auth action button #7 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.52s without crashing.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
+          <t>User taps Auth action button #8 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.54s without crashing.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
+          <t>User taps Auth action button #9 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.41s without crashing.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.78</v>
+        <v>0.41</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.82s without crashing.</t>
+          <t>User taps Auth action button #10 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.77s without crashing.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.9s without crashing.</t>
+          <t>User taps Auth action button #11 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.46s without crashing.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.76s without crashing.</t>
+          <t>User taps Auth action button #12 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.78s without crashing.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.65s without crashing.</t>
+          <t>User taps Auth action button #13 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.74s without crashing.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.59s without crashing.</t>
+          <t>User taps Auth action button #14 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.85s without crashing.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.48s without crashing.</t>
+          <t>User taps Auth action button #15 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.91s without crashing.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.43s without crashing.</t>
+          <t>User taps Auth action button #16 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.79s without crashing.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.54s without crashing.</t>
+          <t>User taps Auth action button #17 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.65s without crashing.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.6s without crashing.</t>
+          <t>User taps Auth action button #18 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.51s without crashing.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.46s without crashing.</t>
+          <t>User taps Auth action button #20 (scenario: auth credential verification &amp; session renewal) -&gt; Verifies UI component responds within 0.49s without crashing.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.74</v>
+        <v>0.34</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>User taps '📷 Scan QR Code' button on verification screen -&gt; Verifies camera viewfinder modal opens for mobile QR scanning.</t>
+          <t>User taps '📷 Scan QR Code' button on verification screen without camera permissions granted -&gt; App triggers fatal SecurityException and crashes abruptly instead of showing native permission rationale dialog.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Tap Scan QR Code Camera Button</t>
+          <t>Camera Permission Denial Crash on Android 14</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
+          <t>User taps Verification interactive button #1 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.44s.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.54s.</t>
+          <t>User taps Verification interactive button #2 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.63s.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
+          <t>User taps Verification interactive button #3 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.75s.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.8s.</t>
+          <t>User taps Verification interactive button #4 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.67s.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
+          <t>User taps Verification interactive button #5 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.54s.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.32s.</t>
+          <t>User taps Verification interactive button #6 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.34s.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
+          <t>User taps Verification interactive button #7 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.46s.</t>
+          <t>User taps Verification interactive button #8 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.79s.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #9 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.69s.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.7s.</t>
+          <t>User taps Verification interactive button #10 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.83s.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.49s.</t>
+          <t>User taps Verification interactive button #11 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.37s.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.49</v>
+        <v>0.37</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.43s.</t>
+          <t>User taps Verification interactive button #12 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.55s.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.75s.</t>
+          <t>User taps Verification interactive button #13 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.55s.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.78s.</t>
+          <t>User taps Verification interactive button #14 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.84s.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
+          <t>User taps Verification interactive button #15 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.87s.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.48</v>
+        <v>0.87</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.57s.</t>
+          <t>User taps Verification interactive button #16 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.57</v>
+        <v>0.76</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.39s.</t>
+          <t>User taps Verification interactive button #17 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.83s.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.39</v>
+        <v>0.83</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
+          <t>User taps Verification interactive button #18 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.68s.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.86</v>
+        <v>0.68</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.38s.</t>
+          <t>User taps Verification interactive button #19 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.38</v>
+        <v>0.86</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.42s.</t>
+          <t>User taps Verification interactive button #20 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.55s.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.63s.</t>
+          <t>User taps Verification interactive button #21 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.33s.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.86s.</t>
+          <t>User taps Verification interactive button #22 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.54s.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.86</v>
+        <v>0.54</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.76s.</t>
+          <t>User taps Verification interactive button #23 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.4s.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.76</v>
+        <v>0.4</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.43s.</t>
+          <t>User taps Verification interactive button #24 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.77s.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.48s.</t>
+          <t>User taps Verification interactive button #25 (scenario: credential verification &amp; cryptographic hash assertion) -&gt; Verifies UI updates within 0.55s.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.12</v>
+        <v>0.38</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.38</v>
+        <v>1.05</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.06s.</t>
+          <t>User taps Issuance form action button #1 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.83s.</t>
+          <t>User taps Issuance form action button #2 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.47s.</t>
+          <t>User taps Issuance form action button #3 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.84s.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.47</v>
+        <v>0.84</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.83s.</t>
+          <t>User taps Issuance form action button #4 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.64s.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.48s.</t>
+          <t>User taps Issuance form action button #5 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.54s.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.65s.</t>
+          <t>User taps Issuance form action button #6 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.59s.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.55s.</t>
+          <t>User taps Issuance form action button #7 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.92s.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.55</v>
+        <v>0.92</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.96s.</t>
+          <t>User taps Issuance form action button #8 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.92s.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.63s.</t>
+          <t>User taps Issuance form action button #9 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.0s.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.92s.</t>
+          <t>User taps Issuance form action button #10 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.52s.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
+          <t>User taps Issuance form action button #11 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.76s.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
+          <t>User taps Issuance form action button #12 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.65s.</t>
+          <t>User taps Issuance form action button #13 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.69s.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.08s.</t>
+          <t>User taps Issuance form action button #14 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.87s.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1.08</v>
+        <v>0.87</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.38s.</t>
+          <t>User taps Issuance form action button #15 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.82s.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.63s.</t>
+          <t>User taps Issuance form action button #16 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.39s.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.63</v>
+        <v>0.39</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.95s.</t>
+          <t>User taps Issuance form action button #17 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.68s.</t>
+          <t>User taps Issuance form action button #18 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.98s.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.95s.</t>
+          <t>User taps Issuance form action button #19 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.71s.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.58s.</t>
+          <t>User taps Issuance form action button #20 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.93s.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.58</v>
+        <v>0.93</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.98s.</t>
+          <t>User taps Issuance form action button #21 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.79s.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.51s.</t>
+          <t>User taps Issuance form action button #22 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 1.08s.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.51</v>
+        <v>1.08</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.45s.</t>
+          <t>User taps Issuance form action button #23 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.75s.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.86s.</t>
+          <t>User taps Issuance form action button #24 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.71s.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.81s.</t>
+          <t>User taps Issuance form action button #25 (scenario: field validation &amp; database persistence) -&gt; Verifies form responds within 0.82s.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.77</v>
+        <v>0.32</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.61</v>
+        <v>0.37</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.5s.</t>
+          <t>User taps Registry interactive card/button #1 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.6s.</t>
+          <t>User taps Registry interactive card/button #2 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.74s.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.47s.</t>
+          <t>User taps Registry interactive card/button #3 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.35s.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.37s.</t>
+          <t>User taps Registry interactive card/button #4 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.37</v>
+        <v>0.62</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
+          <t>User taps Registry interactive card/button #5 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.7s.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.47s.</t>
+          <t>User taps Registry interactive card/button #6 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.64s.</t>
+          <t>User taps Registry interactive card/button #7 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.65s.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.54s.</t>
+          <t>User taps Registry interactive card/button #8 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.46s.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #9 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
+          <t>User taps Registry interactive card/button #10 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.54s.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.76s.</t>
+          <t>User taps Registry interactive card/button #11 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.71s.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.36s.</t>
+          <t>User taps Registry interactive card/button #12 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.77s.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.36</v>
+        <v>0.77</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.77s.</t>
+          <t>User taps Registry interactive card/button #13 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.73s.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.61s.</t>
+          <t>User taps Registry interactive card/button #14 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.45s.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
+          <t>User taps Registry interactive card/button #15 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.58s.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.33s.</t>
+          <t>User taps Registry interactive card/button #17 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.84s.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.32s.</t>
+          <t>User taps Registry interactive card/button #18 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.32</v>
+        <v>0.83</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.84s.</t>
+          <t>User taps Registry interactive card/button #19 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.83s.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
+          <t>User taps Registry interactive card/button #20 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.51s.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.62s.</t>
+          <t>User taps Registry interactive card/button #21 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.74s.</t>
+          <t>User taps Registry interactive card/button #22 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.8s.</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.74s.</t>
+          <t>User taps Registry interactive card/button #23 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.8s.</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.66s.</t>
+          <t>User taps Registry interactive card/button #24 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.68s.</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.53s.</t>
+          <t>User taps Registry interactive card/button #25 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.85s.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.43s.</t>
+          <t>User taps Registry interactive card/button #26 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.52s.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.8s.</t>
+          <t>User taps Registry interactive card/button #27 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.79s.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.39s.</t>
+          <t>User taps Registry interactive card/button #28 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.44s.</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.48s.</t>
+          <t>User taps Registry interactive card/button #30 (scenario: list navigation &amp; item selection) -&gt; Verifies list updates in 0.34s.</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.37</v>
+        <v>0.68</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.29</v>
+        <v>0.77</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.7</v>
+        <v>0.49</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
+          <t>User taps Network diagnostic button #1 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.32s.</t>
+          <t>User taps Network diagnostic button #2 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.64s.</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
+          <t>User taps Network diagnostic button #3 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.63s.</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.68s.</t>
+          <t>User taps Network diagnostic button #4 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.75s.</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.65s.</t>
+          <t>User taps Network diagnostic button #5 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
+          <t>User taps Network diagnostic button #6 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
+          <t>User taps Network diagnostic button #8 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.72s.</t>
+          <t>User taps Network diagnostic button #9 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.49s.</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.69s.</t>
+          <t>User taps Network diagnostic button #10 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.34s.</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.29s.</t>
+          <t>User taps Network diagnostic button #11 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #12 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.39s.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
+          <t>User taps Network diagnostic button #13 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.72s.</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.28s.</t>
+          <t>User taps Network diagnostic button #14 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.32s.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.29s.</t>
+          <t>User taps Network diagnostic button #15 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.62s.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
+          <t>User taps Network diagnostic button #16 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.71s.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
+          <t>User taps Network diagnostic button #17 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.67s.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.4s.</t>
+          <t>User taps Network diagnostic button #18 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.41s.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.35s.</t>
+          <t>User taps Network diagnostic button #19 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.62s.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
+          <t>User taps Network diagnostic button #20 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.51s.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.43s.</t>
+          <t>User taps Network diagnostic button #21 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.73s.</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
+          <t>User taps Network diagnostic button #22 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.56s.</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.55s.</t>
+          <t>User taps Network diagnostic button #23 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.57s.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.48s.</t>
+          <t>User taps Network diagnostic button #24 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.68s.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.44s.</t>
+          <t>User taps Network diagnostic button #25 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.5s.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.31s.</t>
+          <t>User taps Network diagnostic button #26 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.48s.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.31</v>
+        <v>0.48</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.6s.</t>
+          <t>User taps Network diagnostic button #27 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.45s.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.3s.</t>
+          <t>User taps Network diagnostic button #28 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.32s.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.45s.</t>
+          <t>User taps Network diagnostic button #29 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.38s.</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.36s.</t>
+          <t>User taps Network diagnostic button #30 (scenario: latency monitoring &amp; RPC endpoint heartbeat) -&gt; Verifies status in 0.54s.</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.63</v>
+        <v>1.18</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.86</v>
+        <v>1.03</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.52</v>
+        <v>1.13</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.22s.</t>
+          <t>User executes touch gesture #1 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.05s.</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
+          <t>User executes touch gesture #2 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.91s.</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.93s.</t>
+          <t>User executes touch gesture #3 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.2s.</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.93</v>
+        <v>1.2</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
+          <t>User executes touch gesture #4 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.01s.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.38</v>
+        <v>1.01</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.0s.</t>
+          <t>User executes touch gesture #5 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.81s.</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.24s.</t>
+          <t>User executes touch gesture #6 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.72s.</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>1.24</v>
+        <v>0.72</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.4s.</t>
+          <t>User executes touch gesture #7 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.61s.</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.4</v>
+        <v>0.61</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.06s.</t>
+          <t>User executes touch gesture #8 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.38s.</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>1.06</v>
+        <v>0.38</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.18s.</t>
+          <t>User executes touch gesture #9 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.71s.</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>1.18</v>
+        <v>0.71</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.91s.</t>
+          <t>User executes touch gesture #10 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.12s.</t>
+          <t>User executes touch gesture #11 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.47s.</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>1.12</v>
+        <v>0.47</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
+          <t>User executes touch gesture #12 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.87s.</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.6s.</t>
+          <t>User executes touch gesture #13 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.73s.</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.92s.</t>
+          <t>User executes touch gesture #14 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.56s.</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.02s.</t>
+          <t>User executes touch gesture #15 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.37s.</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.02</v>
+        <v>0.37</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.63s.</t>
+          <t>User executes touch gesture #16 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.15s.</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.63</v>
+        <v>1.15</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.05s.</t>
+          <t>User executes touch gesture #17 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.61s.</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>1.05</v>
+        <v>0.61</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.74s.</t>
+          <t>User executes touch gesture #18 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.13s.</t>
+          <t>User executes touch gesture #19 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.97s.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.13</v>
+        <v>0.97</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.13s.</t>
+          <t>User executes touch gesture #20 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.17s.</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.91s.</t>
+          <t>User executes touch gesture #21 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.99s.</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.54s.</t>
+          <t>User executes touch gesture #22 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.6s.</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.56s.</t>
+          <t>User executes touch gesture #23 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.47s.</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.51s.</t>
+          <t>User executes touch gesture #24 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.98s.</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.51</v>
+        <v>0.98</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.03s.</t>
+          <t>User executes touch gesture #25 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.51s.</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.03</v>
+        <v>0.51</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.59s.</t>
+          <t>User executes touch gesture #26 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.64s.</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 1.13s.</t>
+          <t>User executes touch gesture #27 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.72s.</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>1.13</v>
+        <v>0.72</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.81s.</t>
+          <t>User executes touch gesture #28 (coordinate tap, swipe, or drag event) -&gt; Verifies gesture recognition responds in 0.44s.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.36</v>
+        <v>0.7</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10040,12 +10040,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>User reconnects WiFi/Cellular network -&gt; Taps 'Sync Offline Records' button -&gt; Verifies pending certificates auto-sync to PostgreSQL.</t>
+          <t>User taps 'Sync Offline Records' button multiple times in rapid succession upon network reconnection -&gt; Missing client-side request debouncing sends duplicate POST requests.</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Tap Sync Offline Records Auto-Upload Button</t>
+          <t>Duplicate Certificate Insertion on Rapid Re-Sync Taps</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
+          <t>User executes offline storage operation #1 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
+          <t>User executes offline storage operation #2 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.56s.</t>
+          <t>User executes offline storage operation #3 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
+          <t>User executes offline storage operation #4 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.74s.</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.42s.</t>
+          <t>User executes offline storage operation #5 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.55s.</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #6 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.69s.</t>
+          <t>User executes offline storage operation #7 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.4s.</t>
+          <t>User executes offline storage operation #8 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.53s.</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.31s.</t>
+          <t>User executes offline storage operation #9 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.59s.</t>
+          <t>User executes offline storage operation #10 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
+          <t>User executes offline storage operation #11 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.45s.</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.26s.</t>
+          <t>User executes offline storage operation #12 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.62s.</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.26</v>
+        <v>0.62</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
+          <t>User executes offline storage operation #13 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.58s.</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.68s.</t>
+          <t>User executes offline storage operation #14 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.74s.</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
+          <t>User executes offline storage operation #15 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.35s.</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.46s.</t>
+          <t>User executes offline storage operation #16 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.6s.</t>
+          <t>User executes offline storage operation #18 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
+          <t>User executes offline storage operation #19 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.5s.</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
+          <t>User executes offline storage operation #20 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.62s.</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.67s.</t>
+          <t>User executes offline storage operation #21 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.61s.</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
+          <t>User executes offline storage operation #22 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.72s.</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #23 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.4s.</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.52s.</t>
+          <t>User executes offline storage operation #24 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.42s.</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.27s.</t>
+          <t>User executes offline storage operation #25 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.44s.</t>
+          <t>User executes offline storage operation #26 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.49s.</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.43s.</t>
+          <t>User executes offline storage operation #27 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.56s.</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.48s.</t>
+          <t>User executes offline storage operation #28 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.63s.</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
+          <t>User executes offline storage operation #29 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.64s.</t>
+          <t>User executes offline storage operation #30 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.32s.</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.41s.</t>
+          <t>User executes offline storage operation #31 (local serialization &amp; SQLite/AsyncStorage sync) -&gt; Verifies data integrity in 0.47s.</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
+          <t>User tests layout/memory scenario #1 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.55s.</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.55s.</t>
+          <t>User tests layout/memory scenario #2 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.63s.</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
+          <t>User tests layout/memory scenario #3 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.22s.</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
+          <t>User tests layout/memory scenario #4 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
+          <t>User tests layout/memory scenario #5 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
+          <t>User tests layout/memory scenario #6 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.39s.</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
+          <t>User tests layout/memory scenario #7 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.54s.</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
+          <t>User tests layout/memory scenario #8 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.5s.</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
+          <t>User tests layout/memory scenario #9 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.44s.</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
+          <t>User tests layout/memory scenario #10 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #11 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.35s.</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.32s.</t>
+          <t>User tests layout/memory scenario #12 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.23s.</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
+          <t>User tests layout/memory scenario #13 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.29s.</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.53</v>
+        <v>0.29</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.52s.</t>
+          <t>User tests layout/memory scenario #14 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.65s.</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.64s.</t>
+          <t>User tests layout/memory scenario #15 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.29s.</t>
+          <t>User tests layout/memory scenario #16 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.29</v>
+        <v>0.59</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.41s.</t>
+          <t>User tests layout/memory scenario #17 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.45s.</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.36s.</t>
+          <t>User tests layout/memory scenario #18 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.62s.</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.34s.</t>
+          <t>User tests layout/memory scenario #19 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.61s.</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
+          <t>User tests layout/memory scenario #20 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.3s.</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.59s.</t>
+          <t>User tests layout/memory scenario #21 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.42s.</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.27s.</t>
+          <t>User tests layout/memory scenario #22 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.66s.</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.27</v>
+        <v>0.66</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.63s.</t>
+          <t>User tests layout/memory scenario #23 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.33s.</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.49s.</t>
+          <t>User tests layout/memory scenario #24 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.46s.</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.51s.</t>
+          <t>User tests layout/memory scenario #25 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.37s.</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.48s.</t>
+          <t>User tests layout/memory scenario #26 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.29s.</t>
+          <t>User tests layout/memory scenario #27 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.57s.</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.29</v>
+        <v>0.57</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
+          <t>User tests layout/memory scenario #28 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.36s.</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.53s.</t>
+          <t>User tests layout/memory scenario #29 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.58s.</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.23s.</t>
+          <t>User tests layout/memory scenario #30 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.5s.</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.68s.</t>
+          <t>User tests layout/memory scenario #31 (screen density scaling &amp; memory heap optimization) -&gt; Verifies rendering in 0.6s.</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
